--- a/templates/Rechnung_Vorlage.xlsx
+++ b/templates/Rechnung_Vorlage.xlsx
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle4" displayName="Tabelle4" ref="A30:E42" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5">
-  <autoFilter ref="A30:E42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle4" displayName="Tabelle4" ref="A30:E46" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5">
+  <autoFilter ref="A30:E46">
     <filterColumn colId="0" hiddenButton="1" showButton="1"/>
     <filterColumn colId="1" hiddenButton="1" showButton="1"/>
     <filterColumn colId="2" hiddenButton="1" showButton="1"/>

--- a/templates/Rechnung_Vorlage.xlsx
+++ b/templates/Rechnung_Vorlage.xlsx
@@ -18,14 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-407]_-;\-* #,##0.00\ [$€-407]_-;_-* &quot;-&quot;??\ [$€-407]_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="166" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
     <numFmt numFmtId="167" formatCode="[&lt;=9999999]###\-####;\(###\)\ ###\-####"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00;[Red](#,##0.00)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -171,8 +170,24 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F497D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -197,8 +212,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -285,6 +310,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="001F497D"/>
+      </top>
+    </border>
+    <border>
+      <top style="double">
+        <color rgb="001F497D"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
@@ -303,7 +338,7 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -452,6 +487,34 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -598,26 +661,6 @@
     <clientData/>
   </twoCellAnchor>
 </wsDr>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle4" displayName="Tabelle4" ref="A30:E46" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5">
-  <autoFilter ref="A30:E46">
-    <filterColumn colId="0" hiddenButton="1" showButton="1"/>
-    <filterColumn colId="1" hiddenButton="1" showButton="1"/>
-    <filterColumn colId="2" hiddenButton="1" showButton="1"/>
-    <filterColumn colId="3" hiddenButton="1" showButton="1"/>
-    <filterColumn colId="4" hiddenButton="1" showButton="1"/>
-  </autoFilter>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Pos." dataDxfId="3"/>
-    <tableColumn id="2" name="Bezeichnung" dataDxfId="2"/>
-    <tableColumn id="3" name="Menge" dataDxfId="1"/>
-    <tableColumn id="5" name="Einzelpreis"/>
-    <tableColumn id="4" name="Gesamtpreis" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -921,13 +964,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A2:E58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col width="5.42578125" customWidth="1" min="1" max="1"/>
-    <col width="41.42578125" customWidth="1" min="2" max="2"/>
-    <col width="12.7109375" customWidth="1" min="3" max="4"/>
-    <col width="23.7109375" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1"/>
@@ -939,7 +983,6 @@
       <c r="A3" s="53" t="n"/>
       <c r="D3" s="53" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5" ht="9.75" customHeight="1">
       <c r="A5" s="56" t="inlineStr">
         <is>
@@ -1003,7 +1046,6 @@
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="29" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="E14" s="24" t="n"/>
     </row>
@@ -1013,7 +1055,6 @@
     <row r="16" ht="15.75" customHeight="1">
       <c r="E16" s="7" t="n"/>
     </row>
-    <row r="17"/>
     <row r="18" ht="15.75" customHeight="1">
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -1087,279 +1128,279 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29"/>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="74" t="inlineStr">
         <is>
           <t>Pos.</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="74" t="inlineStr">
         <is>
           <t>Bezeichnung</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C30" s="74" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D30" s="74" t="inlineStr">
         <is>
           <t>Einzelpreis</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="75" t="inlineStr">
         <is>
           <t>Gesamtpreis</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="76" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B31" s="23" t="n"/>
-      <c r="C31" s="31" t="n"/>
-      <c r="D31" s="59" t="n"/>
-      <c r="E31" s="60">
+      <c r="B31" s="77" t="n"/>
+      <c r="C31" s="76" t="n"/>
+      <c r="D31" s="78" t="n"/>
+      <c r="E31" s="79">
         <f>D31*C31</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="76" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B32" s="35" t="n"/>
-      <c r="C32" s="61" t="n"/>
-      <c r="D32" s="62" t="n"/>
-      <c r="E32" s="63">
+      <c r="B32" s="77" t="n"/>
+      <c r="C32" s="76" t="n"/>
+      <c r="D32" s="78" t="n"/>
+      <c r="E32" s="79">
         <f>D32*C32</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="76" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B33" s="23" t="n"/>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="59" t="n"/>
-      <c r="E33" s="60">
+      <c r="B33" s="77" t="n"/>
+      <c r="C33" s="76" t="n"/>
+      <c r="D33" s="78" t="n"/>
+      <c r="E33" s="79">
         <f>D33*C33</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="A34" s="76" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B34" s="40" t="n"/>
-      <c r="C34" s="64" t="n"/>
-      <c r="D34" s="65" t="n"/>
-      <c r="E34" s="66">
+      <c r="B34" s="77" t="n"/>
+      <c r="C34" s="76" t="n"/>
+      <c r="D34" s="78" t="n"/>
+      <c r="E34" s="79">
         <f>D34*C34</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" s="76" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="59" t="n"/>
-      <c r="E35" s="60">
+      <c r="B35" s="77" t="n"/>
+      <c r="C35" s="76" t="n"/>
+      <c r="D35" s="78" t="n"/>
+      <c r="E35" s="79">
         <f>D35*C35</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="39" t="inlineStr">
+      <c r="A36" s="76" t="inlineStr">
         <is>
           <t>6.</t>
         </is>
       </c>
-      <c r="B36" s="40" t="n"/>
-      <c r="C36" s="64" t="n"/>
-      <c r="D36" s="65" t="n"/>
-      <c r="E36" s="66">
+      <c r="B36" s="77" t="n"/>
+      <c r="C36" s="76" t="n"/>
+      <c r="D36" s="78" t="n"/>
+      <c r="E36" s="79">
         <f>D36*C36</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>7.</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n"/>
-      <c r="C37" s="31" t="n"/>
-      <c r="D37" s="59" t="n"/>
-      <c r="E37" s="60">
+      <c r="B37" s="77" t="n"/>
+      <c r="C37" s="76" t="n"/>
+      <c r="D37" s="78" t="n"/>
+      <c r="E37" s="79">
         <f>D37*C37</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="21.75" customHeight="1">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="76" t="inlineStr">
         <is>
           <t>8.</t>
         </is>
       </c>
-      <c r="B38" s="40" t="n"/>
-      <c r="C38" s="64" t="n"/>
-      <c r="D38" s="65" t="n"/>
-      <c r="E38" s="67">
+      <c r="B38" s="77" t="n"/>
+      <c r="C38" s="76" t="n"/>
+      <c r="D38" s="78" t="n"/>
+      <c r="E38" s="80">
         <f>D38*C38</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="21.75" customHeight="1">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" s="76" t="inlineStr">
         <is>
           <t>9.</t>
         </is>
       </c>
-      <c r="B39" s="40" t="n"/>
-      <c r="C39" s="64" t="n"/>
-      <c r="D39" s="65" t="n"/>
-      <c r="E39" s="67">
+      <c r="B39" s="77" t="n"/>
+      <c r="C39" s="76" t="n"/>
+      <c r="D39" s="78" t="n"/>
+      <c r="E39" s="80">
         <f>D39*C39</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="9" customHeight="1">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="76" t="inlineStr">
         <is>
           <t>10.</t>
         </is>
       </c>
-      <c r="B40" s="40" t="n"/>
-      <c r="C40" s="64" t="n"/>
-      <c r="D40" s="65" t="n"/>
-      <c r="E40" s="67">
+      <c r="B40" s="77" t="n"/>
+      <c r="C40" s="76" t="n"/>
+      <c r="D40" s="78" t="n"/>
+      <c r="E40" s="80">
         <f>D40*C40</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="21.75" customHeight="1">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="A41" s="76" t="inlineStr">
         <is>
           <t>11.</t>
         </is>
       </c>
-      <c r="B41" s="40" t="n"/>
-      <c r="C41" s="64" t="n"/>
-      <c r="D41" s="65" t="n"/>
-      <c r="E41" s="67">
+      <c r="B41" s="77" t="n"/>
+      <c r="C41" s="76" t="n"/>
+      <c r="D41" s="78" t="n"/>
+      <c r="E41" s="80">
         <f>D41*C41</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="A42" s="76" t="inlineStr">
         <is>
           <t>12.</t>
         </is>
       </c>
-      <c r="B42" s="40" t="n"/>
-      <c r="C42" s="64" t="n"/>
-      <c r="D42" s="65" t="n"/>
-      <c r="E42" s="67">
+      <c r="B42" s="77" t="n"/>
+      <c r="C42" s="76" t="n"/>
+      <c r="D42" s="78" t="n"/>
+      <c r="E42" s="80">
         <f>D42*C42</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="A43" s="76" t="inlineStr">
         <is>
           <t>13.</t>
         </is>
       </c>
-      <c r="B43" s="35" t="n"/>
-      <c r="C43" s="61" t="n"/>
-      <c r="D43" s="62" t="n"/>
-      <c r="E43" s="68">
+      <c r="B43" s="77" t="n"/>
+      <c r="C43" s="76" t="n"/>
+      <c r="D43" s="78" t="n"/>
+      <c r="E43" s="80">
         <f>D43*C43</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="A44" s="76" t="inlineStr">
         <is>
           <t>14.</t>
         </is>
       </c>
-      <c r="B44" s="35" t="n"/>
-      <c r="C44" s="61" t="n"/>
-      <c r="D44" s="62" t="n"/>
-      <c r="E44" s="68">
+      <c r="B44" s="77" t="n"/>
+      <c r="C44" s="76" t="n"/>
+      <c r="D44" s="78" t="n"/>
+      <c r="E44" s="80">
         <f>D44*C44</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="32.1" customHeight="1">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="A45" s="76" t="inlineStr">
         <is>
           <t>15.</t>
         </is>
       </c>
-      <c r="B45" s="35" t="n"/>
-      <c r="C45" s="61" t="n"/>
-      <c r="D45" s="62" t="n"/>
-      <c r="E45" s="68">
+      <c r="B45" s="77" t="n"/>
+      <c r="C45" s="76" t="n"/>
+      <c r="D45" s="78" t="n"/>
+      <c r="E45" s="80">
         <f>D45*C45</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="A46" s="76" t="inlineStr">
         <is>
           <t>16.</t>
         </is>
       </c>
-      <c r="B46" s="35" t="n"/>
-      <c r="C46" s="61" t="n"/>
-      <c r="D46" s="62" t="n"/>
-      <c r="E46" s="68">
+      <c r="B46" s="77" t="n"/>
+      <c r="C46" s="76" t="n"/>
+      <c r="D46" s="78" t="n"/>
+      <c r="E46" s="80">
         <f>D46*C46</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="49" t="n"/>
-      <c r="C47" s="69" t="inlineStr">
+      <c r="C47" s="81" t="inlineStr">
         <is>
           <t>Nettosumme</t>
         </is>
       </c>
-      <c r="D47" s="29" t="n"/>
-      <c r="E47" s="70">
+      <c r="D47" s="82" t="n"/>
+      <c r="E47" s="83">
         <f>SUM(E31:E46)</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="6" customHeight="1">
       <c r="A48" s="3" t="n"/>
-      <c r="C48" s="71" t="inlineStr">
+      <c r="C48" s="84" t="inlineStr">
         <is>
           <t>zzgl. 19%MwSt.</t>
         </is>
       </c>
-      <c r="E48" s="72">
+      <c r="D48" s="85" t="n"/>
+      <c r="E48" s="86">
         <f>E47*19%</f>
         <v/>
       </c>
@@ -1368,18 +1409,17 @@
       <c r="A49" s="50" t="n"/>
     </row>
     <row r="50">
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="82" t="inlineStr">
         <is>
           <t>Rechnungsbetrag</t>
         </is>
       </c>
-      <c r="E50" s="73">
+      <c r="D50" s="82" t="n"/>
+      <c r="E50" s="87">
         <f>E47+E48</f>
         <v/>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="57" t="inlineStr">
         <is>
@@ -1388,7 +1428,6 @@
       </c>
     </row>
     <row r="54"/>
-    <row r="55"/>
     <row r="56">
       <c r="A56" s="49" t="inlineStr">
         <is>
@@ -1396,7 +1435,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="50" t="inlineStr">
         <is>
@@ -1404,7 +1442,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A27:E28"/>
@@ -1430,8 +1467,5 @@
     <firstFooter/>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>